--- a/RoomServer/wg/data/all_wg_logs/expenses.xlsx
+++ b/RoomServer/wg/data/all_wg_logs/expenses.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1228,6 +1228,584 @@
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>30/12/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Mara</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Kitchen paper</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>12/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Mara</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Toilet paper</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>12/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Mara</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Cleaner</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>17/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Mara</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Dish soap</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>17/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>garlic - 2</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>22/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Gloves for cooking</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>27/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Big trash bags</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>29/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Small trash bags</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>29/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Hand soap</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>29/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>salt - 2</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>31/01/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Sugar</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Dish washer</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>26/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Kitchen Papers</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>26/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Hand Soap</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>26/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Toilet paper</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>28/05/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>onions
+dish washing liquid</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>05/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>garlic</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>05/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>oil</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>09/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>sugar</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>09/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>2 big garbage bag - 1.30
+2 small garbage bag - 2.98
+kitchen towel - 2.75</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>11/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>onions</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>12/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>14/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Mara</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>15.87</v>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>WG stuff</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>22/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Sponge</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>29/06/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Natchaya</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>29/06/26</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1856,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>29.74</v>
+        <v>52.45</v>
       </c>
     </row>
     <row r="4">
@@ -1298,7 +1876,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>12.38</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="6">
@@ -1308,7 +1886,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>19.43</v>
+        <v>45.33</v>
       </c>
     </row>
   </sheetData>
